--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487595_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487595_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5726</v>
+        <v>1.4217</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9445</v>
+        <v>1.7663</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3719</v>
+        <v>-0.3446</v>
       </c>
       <c r="G2" t="n">
         <v>1.4081</v>
@@ -610,13 +610,13 @@
         <v>2.5224</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7281</v>
+        <v>-0.879</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.5142</v>
+        <v>-0.6923</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.214</v>
+        <v>-0.1867</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6597</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. NUEZ DIAZ</t>
+          <t>A. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0902</v>
+        <v>-0.1533</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.424</v>
+        <v>0.007</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3337</v>
+        <v>-0.1602</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0725</v>
+        <v>-0.6269</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.206</v>
+        <v>-1.1897</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1335</v>
+        <v>0.5628</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1.3391</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1.2935</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.0456</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0725</v>
+        <v>-1.966</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.206</v>
+        <v>-2.4832</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1335</v>
+        <v>0.5172</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3881</v>
+        <v>1.7463</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5644</v>
+        <v>-0.5846</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5462</v>
+        <v>-0.6441</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0182</v>
+        <v>0.0595</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. MARTIN GONZALEZ</t>
+          <t>A. NUEZ DIAZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3318</v>
+        <v>-0.4634</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0465</v>
+        <v>-0.8244</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3783</v>
+        <v>0.361</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6269</v>
+        <v>-0.0725</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1897</v>
+        <v>-0.206</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5628</v>
+        <v>0.1335</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3391</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2935</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0456</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.966</v>
+        <v>-0.0725</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.4832</v>
+        <v>-0.206</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5172</v>
+        <v>0.1335</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7761</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7463</v>
+        <v>0.3881</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7631</v>
+        <v>0.1912</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6046</v>
+        <v>0.1458</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1586</v>
+        <v>0.0454</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5935</v>
+        <v>-1.3304</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.8056</v>
+        <v>-2.4062</v>
       </c>
       <c r="F5" t="n">
-        <v>1.212</v>
+        <v>1.0758</v>
       </c>
       <c r="G5" t="n">
         <v>-2.1628</v>
@@ -844,13 +844,13 @@
         <v>1.1642</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3095</v>
+        <v>-0.4273</v>
       </c>
       <c r="T5" t="n">
-        <v>0.729</v>
+        <v>0.1284</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4194</v>
+        <v>-0.5557</v>
       </c>
       <c r="V5" t="n">
         <v>0.0955</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1179</v>
+        <v>-1.6241</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2312</v>
+        <v>-1.4103</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1133</v>
+        <v>-0.2138</v>
       </c>
       <c r="G6" t="n">
         <v>-2.4123</v>
@@ -922,13 +922,13 @@
         <v>0.5821</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9944</v>
+        <v>0.4882</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0011</v>
+        <v>-0.1781</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9933</v>
+        <v>0.6662</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2821</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. JIMENEZ HERNANDEZ</t>
+          <t>A. SANTANA OJEDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1777</v>
+        <v>-2.0242</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9745</v>
+        <v>0.4269</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.1522</v>
+        <v>-2.4511</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.5766</v>
+        <v>0.5276</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.208</v>
+        <v>-0.6097</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3686</v>
+        <v>1.1372</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06270000000000001</v>
+        <v>2.7541</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6096</v>
+        <v>0.1153</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6724</v>
+        <v>2.6388</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.6393</v>
+        <v>-2.2266</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5983</v>
+        <v>-0.725</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.041</v>
+        <v>-1.5015</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5821</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5821</v>
+        <v>0.9702</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0989</v>
+        <v>-0.3578</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9118000000000001</v>
+        <v>-0.387</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1871</v>
+        <v>0.0292</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. VIDAL RODRIGUEZ</t>
+          <t>E. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2096</v>
+        <v>-2.3453</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.971</v>
+        <v>-0.9021</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2385</v>
+        <v>-1.4432</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8187</v>
+        <v>-1.266</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4072</v>
+        <v>-2.6875</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4115</v>
+        <v>1.4214</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3048</v>
+        <v>0.7553</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3048</v>
+        <v>-0.5437</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.2991</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5139</v>
+        <v>-2.0214</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1023</v>
+        <v>-2.1437</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4115</v>
+        <v>0.1223</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7761</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R8" t="n">
-        <v>0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6673</v>
+        <v>-1.0792</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3039</v>
+        <v>-0.6873</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3634</v>
+        <v>-0.392</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. VIDAL RODRIGUEZ</t>
+          <t>A. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5332</v>
+        <v>-2.3492</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0627</v>
+        <v>-1.1107</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4705</v>
+        <v>-1.2385</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.266</v>
+        <v>-1.8187</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.6875</v>
+        <v>-1.4072</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4214</v>
+        <v>-0.4115</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7553</v>
+        <v>-0.3048</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5437</v>
+        <v>-0.3048</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2991</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0214</v>
+        <v>-1.5139</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.1437</v>
+        <v>-1.1023</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1223</v>
+        <v>-0.4115</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9702</v>
+        <v>0.194</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2672</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8479</v>
+        <v>0.1643</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4192</v>
+        <v>0.3634</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SANTANA OJEDA</t>
+          <t>J. JIMENEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7214</v>
+        <v>-2.9636</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2158</v>
+        <v>0.2158</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5056</v>
+        <v>-3.1794</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5276</v>
+        <v>-3.5766</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6097</v>
+        <v>-2.208</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1372</v>
+        <v>-1.3686</v>
       </c>
       <c r="J10" t="n">
-        <v>2.7541</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1153</v>
+        <v>-0.6096</v>
       </c>
       <c r="L10" t="n">
-        <v>2.6388</v>
+        <v>0.6724</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2266</v>
+        <v>-3.6393</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.725</v>
+        <v>-1.5983</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5015</v>
+        <v>-2.041</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.055</v>
+        <v>0.3129</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0296</v>
+        <v>0.1531</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0253</v>
+        <v>0.1598</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4466</v>
+        <v>-3.7492</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.279</v>
+        <v>-2.718</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1675</v>
+        <v>-1.0312</v>
       </c>
       <c r="G11" t="n">
         <v>-1.803</v>
@@ -1312,13 +1312,13 @@
         <v>1.3582</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4973</v>
+        <v>-0.8</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1508</v>
+        <v>-0.5897</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3465</v>
+        <v>-0.2103</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5642</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.2391</v>
+        <v>-4.8267</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8393</v>
+        <v>-1.8357</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3998</v>
+        <v>-2.991</v>
       </c>
       <c r="G12" t="n">
         <v>-3.1739</v>
@@ -1390,13 +1390,13 @@
         <v>1.1642</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.0547</v>
+        <v>-0.6424</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.393</v>
+        <v>-0.3895</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6617</v>
+        <v>-0.2529</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2343</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.8253</v>
+        <v>-7.7916</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.0046</v>
+        <v>-7.5621</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1793</v>
+        <v>-0.2295</v>
       </c>
       <c r="G13" t="n">
         <v>-2.5447</v>
@@ -1468,13 +1468,13 @@
         <v>1.9403</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1761</v>
+        <v>-0.1424</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7863</v>
+        <v>-0.3438</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6102</v>
+        <v>0.2014</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2239</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-29.7137</v>
+        <v>-28.1993</v>
       </c>
       <c r="E14" t="n">
-        <v>-17.8677</v>
+        <v>-16.3535</v>
       </c>
       <c r="F14" t="n">
-        <v>-11.846</v>
+        <v>-11.8457</v>
       </c>
       <c r="G14" t="n">
         <v>-17.5217</v>
@@ -1516,7 +1516,7 @@
         <v>-17.4662</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.05560000000000009</v>
+        <v>-0.05559999999999965</v>
       </c>
       <c r="J14" t="n">
         <v>2.0486</v>
@@ -1537,7 +1537,7 @@
         <v>-5.5891</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.910400000000001</v>
+        <v>-2.9104</v>
       </c>
       <c r="Q14" t="n">
         <v>-16.4929</v>
@@ -1546,16 +1546,16 @@
         <v>13.5823</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.907</v>
+        <v>-3.3927</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.8344</v>
+        <v>-3.3202</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.07250000000000012</v>
+        <v>-0.0726999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.374700000000001</v>
+        <v>-4.3747</v>
       </c>
       <c r="W14" t="n">
         <v>1.4104</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.035299999999999</v>
+        <v>7.7087</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3636</v>
+        <v>4.6639</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6716</v>
+        <v>3.0448</v>
       </c>
       <c r="G15" t="n">
         <v>4.7385</v>
@@ -1624,13 +1624,13 @@
         <v>2.1344</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5684</v>
+        <v>1.2419</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.35</v>
+        <v>-0.0497</v>
       </c>
       <c r="U15" t="n">
-        <v>1.9184</v>
+        <v>1.2915</v>
       </c>
       <c r="V15" t="n">
         <v>0.5642</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. MANZANERO CAMACHO</t>
+          <t>N. LASUNCION MARIBLANCA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.2603</v>
+        <v>6.232</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3474</v>
+        <v>4.8157</v>
       </c>
       <c r="F16" t="n">
-        <v>3.913</v>
+        <v>1.4163</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7268</v>
+        <v>5.2571</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1777</v>
+        <v>3.0821</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4509</v>
+        <v>2.175</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2614</v>
+        <v>5.3426</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0226</v>
+        <v>2.072</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7613</v>
+        <v>3.2706</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4654</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>1.155</v>
+        <v>1.01</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6896</v>
+        <v>-1.0956</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9403</v>
+        <v>-0.194</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9403</v>
+        <v>1.7463</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7947</v>
+        <v>-0.337</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2875</v>
+        <v>-0.3746</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5072</v>
+        <v>0.0376</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7985</v>
+        <v>1.506</v>
       </c>
       <c r="W16" t="n">
-        <v>0.7985</v>
+        <v>1.788</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. LASUNCION MARIBLANCA</t>
+          <t>D. MANZANERO CAMACHO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.3137</v>
+        <v>6.1597</v>
       </c>
       <c r="E17" t="n">
-        <v>4.4153</v>
+        <v>2.5466</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8984</v>
+        <v>3.6132</v>
       </c>
       <c r="G17" t="n">
-        <v>5.2571</v>
+        <v>1.7268</v>
       </c>
       <c r="H17" t="n">
-        <v>3.0821</v>
+        <v>3.1777</v>
       </c>
       <c r="I17" t="n">
-        <v>2.175</v>
+        <v>-1.4509</v>
       </c>
       <c r="J17" t="n">
-        <v>5.3426</v>
+        <v>1.2614</v>
       </c>
       <c r="K17" t="n">
-        <v>2.072</v>
+        <v>2.0226</v>
       </c>
       <c r="L17" t="n">
-        <v>3.2706</v>
+        <v>-0.7613</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.08550000000000001</v>
+        <v>0.4654</v>
       </c>
       <c r="N17" t="n">
-        <v>1.01</v>
+        <v>1.155</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0956</v>
+        <v>-0.6896</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.194</v>
+        <v>1.9403</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7463</v>
+        <v>1.9403</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2553</v>
+        <v>1.6941</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.775</v>
+        <v>0.4867</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4802</v>
+        <v>1.2074</v>
       </c>
       <c r="V17" t="n">
-        <v>1.506</v>
+        <v>0.7985</v>
       </c>
       <c r="W17" t="n">
-        <v>1.788</v>
+        <v>0.7985</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.6966</v>
+        <v>4.5514</v>
       </c>
       <c r="E18" t="n">
-        <v>3.5892</v>
+        <v>4.0897</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1074</v>
+        <v>0.4617</v>
       </c>
       <c r="G18" t="n">
         <v>3.4604</v>
@@ -1858,13 +1858,13 @@
         <v>1.7463</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5399</v>
+        <v>0.3149</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.0323</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0072</v>
+        <v>0.3472</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.974</v>
+        <v>3.4745</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0007</v>
+        <v>1.5012</v>
       </c>
       <c r="F19" t="n">
         <v>1.9732</v>
@@ -1936,10 +1936,10 @@
         <v>1.5523</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3645</v>
+        <v>0.136</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7874</v>
+        <v>-0.2869</v>
       </c>
       <c r="U19" t="n">
         <v>0.4229</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. MARTINEZ ALVAREZ</t>
+          <t>M. KREISLER LORENTE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4174</v>
+        <v>2.4215</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8556</v>
+        <v>-0.7362</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5618</v>
+        <v>3.1577</v>
       </c>
       <c r="G20" t="n">
-        <v>1.9627</v>
+        <v>-0.5668</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8959</v>
+        <v>1.0982</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9332</v>
+        <v>-1.665</v>
       </c>
       <c r="J20" t="n">
-        <v>2.6546</v>
+        <v>-0.8374</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4922</v>
+        <v>1.0834</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1624</v>
+        <v>-1.9208</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6919</v>
+        <v>0.2706</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4037</v>
+        <v>0.0148</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0956</v>
+        <v>0.2558</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.7463</v>
+        <v>1.7463</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1642</v>
+        <v>1.7463</v>
       </c>
       <c r="S20" t="n">
-        <v>1.6368</v>
+        <v>0.9121</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5473</v>
+        <v>0.1012</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0895</v>
+        <v>0.8109</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5642</v>
+        <v>0.3299</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. KREISLER LORENTE</t>
+          <t>E. MARTINEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.2124</v>
+        <v>1.9714</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8363</v>
+        <v>0.3551</v>
       </c>
       <c r="F21" t="n">
-        <v>3.0487</v>
+        <v>1.6163</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5668</v>
+        <v>1.9627</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0982</v>
+        <v>2.8959</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.665</v>
+        <v>-0.9332</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8374</v>
+        <v>2.6546</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0834</v>
+        <v>2.4922</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9208</v>
+        <v>0.1624</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2706</v>
+        <v>-0.6919</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0148</v>
+        <v>0.4037</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2558</v>
+        <v>-1.0956</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7463</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="S21" t="n">
-        <v>0.703</v>
+        <v>1.1908</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0011</v>
+        <v>0.0468</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7019</v>
+        <v>1.144</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3299</v>
+        <v>0.5642</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4916</v>
+        <v>0.1185</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0392</v>
+        <v>-1.4396</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5308</v>
+        <v>1.5581</v>
       </c>
       <c r="G22" t="n">
         <v>0.6897</v>
@@ -2170,13 +2170,13 @@
         <v>2.5224</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4915</v>
+        <v>0.1183</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7413</v>
+        <v>0.3409</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2499</v>
+        <v>-0.2226</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2716</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6876</v>
+        <v>-2.924</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8504</v>
+        <v>-3.9505</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1628</v>
+        <v>1.0266</v>
       </c>
       <c r="G23" t="n">
         <v>-3.4732</v>
@@ -2248,13 +2248,13 @@
         <v>1.9403</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1278</v>
+        <v>-0.3642</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0595</v>
+        <v>-0.1596</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0684</v>
+        <v>-0.2047</v>
       </c>
       <c r="V23" t="n">
         <v>1.8836</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>29.71370000000001</v>
+        <v>29.7137</v>
       </c>
       <c r="E24" t="n">
         <v>11.8459</v>
       </c>
       <c r="F24" t="n">
-        <v>17.8677</v>
+        <v>17.8679</v>
       </c>
       <c r="G24" t="n">
         <v>17.5217</v>
@@ -2305,7 +2305,7 @@
         <v>13.9811</v>
       </c>
       <c r="L24" t="n">
-        <v>5.5892</v>
+        <v>5.589200000000001</v>
       </c>
       <c r="M24" t="n">
         <v>-2.0488</v>
@@ -2329,7 +2329,7 @@
         <v>4.9069</v>
       </c>
       <c r="T24" t="n">
-        <v>0.07250000000000001</v>
+        <v>0.07250000000000004</v>
       </c>
       <c r="U24" t="n">
         <v>4.8342</v>
